--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_1_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_1_True.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>Pg Vm Projection True</t>
   </si>
@@ -31,88 +31,82 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_i_tot</t>
   </si>
   <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
   </si>
   <si>
     <t>cost_tot</t>
   </si>
   <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
     <t>Ibr_to_r_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>0.23s (0.27 s)</t>
-  </si>
-  <si>
-    <t>28678.72 (24469.43 &gt; 17.20%)</t>
-  </si>
-  <si>
-    <t>1.50 (2.45)</t>
-  </si>
-  <si>
-    <t>0.14s (0.27 s)</t>
-  </si>
-  <si>
-    <t>24867.86 (24469.43 &gt; 1.63%)</t>
-  </si>
-  <si>
-    <t>2.24 (2.45)</t>
-  </si>
-  <si>
-    <t>0.28s (0.27 s)</t>
-  </si>
-  <si>
-    <t>24471.46 (24469.43 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>2.45 (2.45)</t>
-  </si>
-  <si>
-    <t>0.17s (0.27 s)</t>
+    <t>0.05s (0.05 s)</t>
+  </si>
+  <si>
+    <t>149.40 (245.00)</t>
+  </si>
+  <si>
+    <t>28673.66 (24469.43 &gt; 17.18%)</t>
+  </si>
+  <si>
+    <t>218.19 (245.00)</t>
+  </si>
+  <si>
+    <t>24984.14 (24469.43 &gt; 2.10%)</t>
+  </si>
+  <si>
+    <t>245.00 (245.00)</t>
+  </si>
+  <si>
+    <t>24468.79 (24469.43 &gt; 0.00%)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +489,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.19112104069743E-17</v>
+        <v>0.008745058439671993</v>
       </c>
       <c r="C2">
-        <v>2.19112104069743E-17</v>
+        <v>3.460742300376296E-05</v>
       </c>
       <c r="D2">
-        <v>2.19112104069743E-17</v>
+        <v>2.246536269012722E-06</v>
       </c>
       <c r="E2">
-        <v>2.19112104069743E-17</v>
+        <v>2.246536269012722E-06</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,50 +506,38 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.9507362246513367</v>
+        <v>8.881538391113281</v>
       </c>
       <c r="C3">
-        <v>0.01024177297949791</v>
+        <v>0.08077900111675262</v>
       </c>
       <c r="D3">
-        <v>8.444463794887724E-09</v>
+        <v>5.546656467458888E-09</v>
       </c>
       <c r="E3">
-        <v>8.444463794887724E-09</v>
+        <v>5.546656467458888E-09</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>8.77687433574903E-19</v>
+        <v>0.0008238165755756199</v>
       </c>
       <c r="C5">
-        <v>8.77687433574903E-19</v>
+        <v>9.908751962939277E-05</v>
       </c>
       <c r="D5">
-        <v>8.77687433574903E-19</v>
+        <v>7.578257168461278E-07</v>
       </c>
       <c r="E5">
-        <v>8.77687433574903E-19</v>
+        <v>7.578257168461278E-07</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +545,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.9366069436073303</v>
+        <v>0.006119314581155777</v>
       </c>
       <c r="C6">
-        <v>0.009690023027360439</v>
+        <v>0.006084566935896873</v>
       </c>
       <c r="D6">
-        <v>3.966290023527108E-06</v>
+        <v>0.00609219167381525</v>
       </c>
       <c r="E6">
-        <v>3.966290023527108E-06</v>
+        <v>0.00609219167381525</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.008329508826136589</v>
-      </c>
-      <c r="C7">
-        <v>4.185397119726986E-05</v>
-      </c>
-      <c r="D7">
-        <v>6.351378942781594E-06</v>
-      </c>
-      <c r="E7">
-        <v>6.351378942781594E-06</v>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,16 +579,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.003987056203186512</v>
+        <v>0.0006421128637157381</v>
       </c>
       <c r="C8">
-        <v>0.003561356104910374</v>
+        <v>9.971891267923638E-05</v>
       </c>
       <c r="D8">
-        <v>0.0009664306417107582</v>
+        <v>7.840753255550226E-07</v>
       </c>
       <c r="E8">
-        <v>0.0009664306417107582</v>
+        <v>7.840753255550226E-07</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -614,16 +596,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.002500270027667284</v>
+        <v>0.01319599151611328</v>
       </c>
       <c r="C9">
-        <v>0.00111020146869123</v>
+        <v>0.008573687635362148</v>
       </c>
       <c r="D9">
-        <v>0.0005154787795618176</v>
+        <v>0.0004426557279657573</v>
       </c>
       <c r="E9">
-        <v>0.0005154787795618176</v>
+        <v>0.0004426557279657573</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,16 +613,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.001286535640247166</v>
+        <v>0.9509320259094238</v>
       </c>
       <c r="C10">
-        <v>0.0001780860184226185</v>
+        <v>0.009764274582266808</v>
       </c>
       <c r="D10">
-        <v>0.0001117682186304592</v>
+        <v>5.842161754365804E-10</v>
       </c>
       <c r="E10">
-        <v>0.0001117682186304592</v>
+        <v>5.842161754365804E-10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -648,16 +630,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.002464934717863798</v>
+        <v>8.77687433574903E-19</v>
       </c>
       <c r="C11">
-        <v>0.0010999875376001</v>
+        <v>8.77687433574903E-19</v>
       </c>
       <c r="D11">
-        <v>0.0005076794186607003</v>
+        <v>8.77687433574903E-19</v>
       </c>
       <c r="E11">
-        <v>0.0005076794186607003</v>
+        <v>8.77687433574903E-19</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,50 +647,50 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.01181335467845201</v>
+        <v>0.003216288285329938</v>
       </c>
       <c r="C12">
-        <v>0.004682852420955896</v>
+        <v>0.00683531491085887</v>
       </c>
       <c r="D12">
-        <v>0.0009072389802895486</v>
+        <v>0.0004266844189260155</v>
       </c>
       <c r="E12">
-        <v>0.0009072389802895486</v>
+        <v>0.0004266844189260155</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
+      <c r="B13">
+        <v>0.9375534653663635</v>
+      </c>
+      <c r="C13">
+        <v>0.009003471583127975</v>
+      </c>
+      <c r="D13">
+        <v>2.348344878555508E-06</v>
+      </c>
+      <c r="E13">
+        <v>2.348344878555508E-06</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" t="s">
-        <v>31</v>
+      <c r="B14">
+        <v>2.19112104069743E-17</v>
+      </c>
+      <c r="C14">
+        <v>2.19112104069743E-17</v>
+      </c>
+      <c r="D14">
+        <v>2.19112104069743E-17</v>
+      </c>
+      <c r="E14">
+        <v>2.19112104069743E-17</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -716,16 +698,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0.346472442150116</v>
+        <v>0.005621337331831455</v>
       </c>
       <c r="C15">
-        <v>0.003534987568855286</v>
+        <v>0.005585749633610249</v>
       </c>
       <c r="D15">
-        <v>4.151156190346228E-06</v>
+        <v>0.005601127631962299</v>
       </c>
       <c r="E15">
-        <v>4.151156190346228E-06</v>
+        <v>0.005601127631962299</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,16 +715,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>8.880167961120605</v>
+        <v>0.2629548609256744</v>
       </c>
       <c r="C16">
-        <v>0.09016094356775284</v>
+        <v>0.2576709389686584</v>
       </c>
       <c r="D16">
-        <v>8.021898878496359E-08</v>
+        <v>0.2574759125709534</v>
       </c>
       <c r="E16">
-        <v>8.021898878496359E-08</v>
+        <v>0.2574759125709534</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,50 +732,67 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.3458100855350494</v>
+        <v>0.124712772667408</v>
       </c>
       <c r="C17">
-        <v>0.003532928880304098</v>
+        <v>0.07164449244737625</v>
       </c>
       <c r="D17">
-        <v>4.161300694249803E-06</v>
+        <v>0.00162029464263469</v>
       </c>
       <c r="E17">
-        <v>4.161300694249803E-06</v>
+        <v>0.00162029464263469</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.001043172902427614</v>
-      </c>
-      <c r="C18">
-        <v>0.0001805796346161515</v>
-      </c>
-      <c r="D18">
-        <v>0.0001137641083914787</v>
-      </c>
-      <c r="E18">
-        <v>0.0001137641083914787</v>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>0.1092550382018089</v>
-      </c>
-      <c r="C19">
-        <v>0.04025879874825478</v>
-      </c>
-      <c r="D19">
-        <v>0.005238823592662811</v>
-      </c>
-      <c r="E19">
-        <v>0.005238823592662811</v>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.2625724971294403</v>
+      </c>
+      <c r="C20">
+        <v>0.2572774887084961</v>
+      </c>
+      <c r="D20">
+        <v>0.2570821046829224</v>
+      </c>
+      <c r="E20">
+        <v>0.2570821046829224</v>
       </c>
     </row>
   </sheetData>
